--- a/data/trans_bre/P1408-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1408-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>-5,77%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,24</t>
+          <t>-2,44; 1,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,74</t>
+          <t>-0,94; 0,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,4</t>
+          <t>-2,59; 0,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,21</t>
+          <t>-1,1; 1,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-83,36; 136,6</t>
+          <t>-81,65; 162,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 182,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-66,24; 231,26</t>
+          <t>-67,38; 176,03</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>25,39%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,88; -0,15</t>
+          <t>-5,13; -0,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 0,29</t>
+          <t>-3,4; 0,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 1,91</t>
+          <t>-0,29; 1,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,64</t>
+          <t>-0,88; 1,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,35; 15,39</t>
+          <t>-86,57; 2,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 252,24</t>
+          <t>-58,0; 252,12</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>100,62%</t>
+          <t>34,86%</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,6</t>
+          <t>-4,05; 3,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,49</t>
+          <t>-3,28; 0,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; -1,06</t>
+          <t>-3,65; -1,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,77</t>
+          <t>-1,71; 4,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 103,73</t>
+          <t>-72,38; 92,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-89,4; 62,09</t>
+          <t>-89,54; 62,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,09; 534,58</t>
+          <t>-46,66; 166,19</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-55,89%</t>
+          <t>-44,49%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,35</t>
+          <t>-3,13; 0,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; -1,54</t>
+          <t>-3,88; -1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; -0,05</t>
+          <t>-2,58; -0,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,23; -0,57</t>
+          <t>-2,7; -0,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 11,39</t>
+          <t>-59,4; 6,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-96,12; -49,5</t>
+          <t>-95,45; -52,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,19; 8,79</t>
+          <t>-78,54; -1,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,65; -24,01</t>
+          <t>-67,51; -4,24</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-20,22%</t>
+          <t>-2,21%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; -2,13</t>
+          <t>-8,01; -1,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,77</t>
+          <t>-1,42; 1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,89</t>
+          <t>-2,25; 1,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,25</t>
+          <t>-2,17; 1,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,95; -35,95</t>
+          <t>-81,69; -27,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 128,76</t>
+          <t>-48,46; 130,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-67,06; 62,94</t>
+          <t>-66,69; 72,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,92; 41,96</t>
+          <t>-40,0; 58,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>1,96</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>492,73%</t>
+          <t>452,35%</t>
         </is>
       </c>
     </row>
@@ -1160,27 +1160,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,16</t>
+          <t>-0,04; 3,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,24</t>
+          <t>0,75; 2,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,41</t>
+          <t>-1,34; 1,45</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,02</t>
+          <t>0,85; 2,9</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 841,27</t>
+          <t>-7,24; 783,2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,86; 444,03</t>
+          <t>-65,63; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51,15; —</t>
+          <t>43,54; —</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-5,13%</t>
+          <t>-3,77%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; -0,57</t>
+          <t>-2,44; -0,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,41</t>
+          <t>-1,58; -0,3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,04</t>
+          <t>-1,37; -0,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,65</t>
+          <t>-0,77; 0,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-51,33; -14,86</t>
+          <t>-50,19; -15,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-62,53; -19,3</t>
+          <t>-62,82; -16,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-56,76; -2,03</t>
+          <t>-58,86; -6,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,89; 33,03</t>
+          <t>-26,28; 25,46</t>
         </is>
       </c>
     </row>
